--- a/SHOP_Qcut_Flow 平均交易時間差.xlsx
+++ b/SHOP_Qcut_Flow 平均交易時間差.xlsx
@@ -413,36 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>SHAP_Min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SHAP_Max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Feature_Mean</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SHAP_Mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SHAP_Median</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SHAP_Std</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Fraud_Prob</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Cnt</t>
         </is>
@@ -450,201 +460,261 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>0.5429999828338623</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3.158600091934204</v>
+      </c>
+      <c r="C2" t="n">
         <v>1724.1186</v>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>1.866400003433228</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>1.831400036811829</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.4505999982357025</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>0.8762999773025513</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>1411</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>0.5430999994277954</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3.039499998092651</v>
+      </c>
+      <c r="C3" t="n">
         <v>6133.8838</v>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>1.564800024032593</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>1.570099949836731</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0.4392000138759613</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>0.8690999746322632</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>0.3095000088214874</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2.440999984741211</v>
+      </c>
+      <c r="C4" t="n">
         <v>15010.5684</v>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>1.428300023078918</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>1.407999992370605</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>0.3495000004768372</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>0.8702999949455261</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>0.1424999982118607</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.835399985313416</v>
+      </c>
+      <c r="C5" t="n">
         <v>25970.1341</v>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>0.8626000285148621</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>0.8337000012397766</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>0.2716000080108643</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>0.8664000034332275</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>1411</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>0.1092000007629395</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.669800043106079</v>
+      </c>
+      <c r="C6" t="n">
         <v>41165.2128</v>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>0.7142999768257141</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>0.7081999778747559</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>0.1876000016927719</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>0.8657000064849854</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>-0.1583999991416931</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.599900007247925</v>
+      </c>
+      <c r="C7" t="n">
         <v>57770.4538</v>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>0.6732000112533569</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>0.6891000270843506</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>0.2522999942302704</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>0.8619999885559082</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>1411</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>-0.5116000175476074</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1.210199952125549</v>
+      </c>
+      <c r="C8" t="n">
         <v>81831.0082</v>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>0.2755999863147736</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>0.2867999970912933</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>0.2326000034809113</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>0.8633000254631042</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>1409</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>-0.8828999996185303</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.05239999294281</v>
+      </c>
+      <c r="C9" t="n">
         <v>115172.5554</v>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>0.1124999970197678</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>0.1242000013589859</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>0.3441999852657318</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>0.8592000007629395</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>1409</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>-0.9945999979972839</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6011000275611877</v>
+      </c>
+      <c r="C10" t="n">
         <v>182265.6025</v>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>-0.274399995803833</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>-0.2885999977588654</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>0.2569000124931335</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>0.8582000136375427</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>1412</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>-2.17960000038147</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4988999962806702</v>
+      </c>
+      <c r="C11" t="n">
         <v>454175.2104</v>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>-0.7634999752044678</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>-0.7426999807357788</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>0.398499995470047</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>0.8587999939918518</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>1409</v>
       </c>
     </row>
